--- a/school_counselor_forms/032_student_technology_usage_survey--school_counselor_forms.xlsx
+++ b/school_counselor_forms/032_student_technology_usage_survey--school_counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>teacher_aided_learning</t>
+          <t>teacher_aided_learning_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teacher Aided Learning</t>
+          <t>Teacher Aided Learning 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>student_independence_in_learning</t>
+          <t>student_independence_in_learning_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>student_self_directed_learning</t>
+          <t>student_self_directed_learning_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>student_self_learning</t>
+          <t>student_self_learning_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>student_device_purpose</t>
+          <t>student_device_purpose_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Device Purpose</t>
+          <t>Student Device Purpose 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Device Purpose</t>
+          <t>Teacher Device Purpose</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Device Use</t>
+          <t>Teacher Device Use</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>student_independence_in_learning</t>
+          <t>student_independence_in_learning_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Independence in Learning</t>
+          <t>Student Independence In Learning 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>teacher_aided_learning_choices</t>
+          <t>teacher_aided_learning_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>teacher_aided_learning_choices</t>
+          <t>teacher_aided_learning_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>student_independence_in_learning_choices</t>
+          <t>student_independence_in_learning_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>student_independence_in_learning_choices</t>
+          <t>student_independence_in_learning_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>student_self_directed_learning_choices</t>
+          <t>student_self_directed_learning_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>student_self_directed_learning_choices</t>
+          <t>student_self_directed_learning_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>student_device_purpose_choices</t>
+          <t>student_device_purpose_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>student_device_purpose_choices</t>
+          <t>student_device_purpose_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>student_independence_in_learning_choices</t>
+          <t>student_independence_in_learning_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>student_independence_in_learning_choices</t>
+          <t>student_independence_in_learning_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
